--- a/outputs/469-9.xlsx
+++ b/outputs/469-9.xlsx
@@ -174,12 +174,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -375,317 +379,272 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>4543.19</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>139001.592</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <f aca="false">IF(C2&gt;0,C2,"")</f>
+      <c r="G2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>4543.19</v>
       </c>
-      <c r="I2" s="0" t="str">
-        <f aca="false">IF(C2&lt;0,ABS(C2),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>28723.2433333333</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>134458.402</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <f aca="false">IF(C3&gt;0,C3,"")</f>
+      <c r="G3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>28723.2433333333</v>
       </c>
-      <c r="I3" s="0" t="str">
-        <f aca="false">IF(C3&lt;0,ABS(C3),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="B4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>21846.3966666667</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>105735.158666667</v>
       </c>
-      <c r="G4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <f aca="false">IF(C4&gt;0,C4,"")</f>
+      <c r="G4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>21846.3966666667</v>
       </c>
-      <c r="I4" s="0" t="str">
-        <f aca="false">IF(C4&lt;0,ABS(C4),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>-6.93333333333333</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>83888.762</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="str">
-        <f aca="false">IF(C5&gt;0,C5,"")</f>
-        <v/>
-      </c>
-      <c r="I5" s="0" t="n">
-        <f aca="false">IF(C5&lt;0,ABS(C5),"")</f>
+      <c r="G5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>6.93333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>3535.258</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>83895.6953333333</v>
       </c>
-      <c r="G6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <f aca="false">IF(C6&gt;0,C6,"")</f>
+      <c r="G6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>3535.258</v>
       </c>
-      <c r="I6" s="0" t="str">
-        <f aca="false">IF(C6&lt;0,ABS(C6),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>-18867.3913333333</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>80360.4373333333</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="0" t="str">
-        <f aca="false">IF(C7&gt;0,C7,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="0" t="n">
-        <f aca="false">IF(C7&lt;0,ABS(C7),"")</f>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>18867.3913333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>866.266666666667</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>99227.8286666667</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <f aca="false">IF(C8&gt;0,C8,"")</f>
+      <c r="G8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>866.266666666667</v>
       </c>
-      <c r="I8" s="0" t="str">
-        <f aca="false">IF(C8&lt;0,ABS(C8),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="B9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>-11314.198</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <v>98361.562</v>
       </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="0" t="str">
-        <f aca="false">IF(C9&gt;0,C9,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="0" t="n">
-        <f aca="false">IF(C9&lt;0,ABS(C9),"")</f>
+      <c r="G9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>11314.198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>-54666.1246666667</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>109675.76</v>
       </c>
-      <c r="G10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="0" t="str">
-        <f aca="false">IF(C10&gt;0,C10,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="0" t="n">
-        <f aca="false">IF(C10&lt;0,ABS(C10),"")</f>
+      <c r="G10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>54666.1246666667</v>
       </c>
     </row>

--- a/outputs/469-9.xlsx
+++ b/outputs/469-9.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t xml:space="preserve">CHEQUE NUMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credits</t>
   </si>
   <si>
     <t xml:space="preserve"> UWE PMT            </t>
@@ -407,12 +401,6 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
@@ -425,10 +413,10 @@
         <v>4543.19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>139001.592</v>
@@ -436,7 +424,7 @@
       <c r="G2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>4543.19</v>
       </c>
     </row>
@@ -451,10 +439,10 @@
         <v>28723.2433333333</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>134458.402</v>
@@ -462,7 +450,7 @@
       <c r="G3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="I3" s="1" t="n">
         <v>28723.2433333333</v>
       </c>
     </row>
@@ -477,10 +465,10 @@
         <v>21846.3966666667</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>105735.158666667</v>
@@ -488,7 +476,7 @@
       <c r="G4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>21846.3966666667</v>
       </c>
     </row>
@@ -503,10 +491,10 @@
         <v>-6.93333333333333</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>83888.762</v>
@@ -514,7 +502,7 @@
       <c r="G5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>6.93333333333333</v>
       </c>
     </row>
@@ -529,10 +517,10 @@
         <v>3535.258</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>83895.6953333333</v>
@@ -540,7 +528,7 @@
       <c r="G6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>3535.258</v>
       </c>
     </row>
@@ -555,10 +543,10 @@
         <v>-18867.3913333333</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>80360.4373333333</v>
@@ -566,7 +554,7 @@
       <c r="G7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>18867.3913333333</v>
       </c>
     </row>
@@ -581,10 +569,10 @@
         <v>866.266666666667</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>99227.8286666667</v>
@@ -592,7 +580,7 @@
       <c r="G8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>866.266666666667</v>
       </c>
     </row>
@@ -607,10 +595,10 @@
         <v>-11314.198</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>98361.562</v>
@@ -618,7 +606,7 @@
       <c r="G9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>11314.198</v>
       </c>
     </row>
@@ -633,10 +621,10 @@
         <v>-54666.1246666667</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>109675.76</v>
@@ -644,7 +632,7 @@
       <c r="G10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>54666.1246666667</v>
       </c>
     </row>
